--- a/artfynd/A 49247-2024 artfynd.xlsx
+++ b/artfynd/A 49247-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123452422</v>
       </c>
       <c r="B2" t="n">
-        <v>92238</v>
+        <v>92244</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 49247-2024 artfynd.xlsx
+++ b/artfynd/A 49247-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123452422</v>
       </c>
       <c r="B2" t="n">
-        <v>92247</v>
+        <v>92264</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 49247-2024 artfynd.xlsx
+++ b/artfynd/A 49247-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123452422</v>
       </c>
       <c r="B2" t="n">
-        <v>92264</v>
+        <v>92269</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 49247-2024 artfynd.xlsx
+++ b/artfynd/A 49247-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123452422</v>
       </c>
       <c r="B2" t="n">
-        <v>92269</v>
+        <v>92271</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
